--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X350"/>
+  <dimension ref="A1:X353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27607,10 +27607,10 @@
         <v>343.67</v>
       </c>
       <c r="C350" t="n">
-        <v>337.86</v>
+        <v>334.19</v>
       </c>
       <c r="D350" t="n">
-        <v>348.74</v>
+        <v>337.77</v>
       </c>
       <c r="E350" t="n">
         <v>323.58</v>
@@ -27670,6 +27670,240 @@
         <v>342.53</v>
       </c>
       <c r="X350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>342.76</v>
+      </c>
+      <c r="C351" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="D351" t="n">
+        <v>330.03</v>
+      </c>
+      <c r="E351" t="n">
+        <v>318.36</v>
+      </c>
+      <c r="F351" t="n">
+        <v>307.83</v>
+      </c>
+      <c r="G351" t="n">
+        <v>308.87</v>
+      </c>
+      <c r="H351" t="n">
+        <v>297.25</v>
+      </c>
+      <c r="I351" t="n">
+        <v>304.9</v>
+      </c>
+      <c r="J351" t="n">
+        <v>300.78</v>
+      </c>
+      <c r="K351" t="n">
+        <v>313.76</v>
+      </c>
+      <c r="L351" t="n">
+        <v>324.8</v>
+      </c>
+      <c r="M351" t="n">
+        <v>305.11</v>
+      </c>
+      <c r="N351" t="n">
+        <v>322.69</v>
+      </c>
+      <c r="O351" t="n">
+        <v>335.01</v>
+      </c>
+      <c r="P351" t="n">
+        <v>335.49</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="R351" t="n">
+        <v>339.43</v>
+      </c>
+      <c r="S351" t="n">
+        <v>350.92</v>
+      </c>
+      <c r="T351" t="n">
+        <v>357.66</v>
+      </c>
+      <c r="U351" t="n">
+        <v>348.73</v>
+      </c>
+      <c r="V351" t="n">
+        <v>354.7</v>
+      </c>
+      <c r="W351" t="n">
+        <v>341.86</v>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>343.02</v>
+      </c>
+      <c r="C352" t="n">
+        <v>329.01</v>
+      </c>
+      <c r="D352" t="n">
+        <v>321.16</v>
+      </c>
+      <c r="E352" t="n">
+        <v>315.14</v>
+      </c>
+      <c r="F352" t="n">
+        <v>304.75</v>
+      </c>
+      <c r="G352" t="n">
+        <v>306.15</v>
+      </c>
+      <c r="H352" t="n">
+        <v>294.21</v>
+      </c>
+      <c r="I352" t="n">
+        <v>300.46</v>
+      </c>
+      <c r="J352" t="n">
+        <v>297.24</v>
+      </c>
+      <c r="K352" t="n">
+        <v>314.87</v>
+      </c>
+      <c r="L352" t="n">
+        <v>325.68</v>
+      </c>
+      <c r="M352" t="n">
+        <v>299.97</v>
+      </c>
+      <c r="N352" t="n">
+        <v>322.69</v>
+      </c>
+      <c r="O352" t="n">
+        <v>336.9</v>
+      </c>
+      <c r="P352" t="n">
+        <v>338.55</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="R352" t="n">
+        <v>341.25</v>
+      </c>
+      <c r="S352" t="n">
+        <v>351.49</v>
+      </c>
+      <c r="T352" t="n">
+        <v>358.49</v>
+      </c>
+      <c r="U352" t="n">
+        <v>350.56</v>
+      </c>
+      <c r="V352" t="n">
+        <v>353.71</v>
+      </c>
+      <c r="W352" t="n">
+        <v>342</v>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>342.91</v>
+      </c>
+      <c r="C353" t="n">
+        <v>330.02</v>
+      </c>
+      <c r="D353" t="n">
+        <v>321.16</v>
+      </c>
+      <c r="E353" t="n">
+        <v>313.02</v>
+      </c>
+      <c r="F353" t="n">
+        <v>303.71</v>
+      </c>
+      <c r="G353" t="n">
+        <v>305.27</v>
+      </c>
+      <c r="H353" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="I353" t="n">
+        <v>299.18</v>
+      </c>
+      <c r="J353" t="n">
+        <v>296.62</v>
+      </c>
+      <c r="K353" t="n">
+        <v>314.09</v>
+      </c>
+      <c r="L353" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="M353" t="n">
+        <v>298.28</v>
+      </c>
+      <c r="N353" t="n">
+        <v>320.43</v>
+      </c>
+      <c r="O353" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="P353" t="n">
+        <v>340.01</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>342.08</v>
+      </c>
+      <c r="R353" t="n">
+        <v>343.47</v>
+      </c>
+      <c r="S353" t="n">
+        <v>352.66</v>
+      </c>
+      <c r="T353" t="n">
+        <v>359.12</v>
+      </c>
+      <c r="U353" t="n">
+        <v>350.24</v>
+      </c>
+      <c r="V353" t="n">
+        <v>353.95</v>
+      </c>
+      <c r="W353" t="n">
+        <v>341.63</v>
+      </c>
+      <c r="X353" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27686,7 +27920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31369,6 +31603,36 @@
       </c>
       <c r="B368" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -31537,28 +31801,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3724507458310898</v>
+        <v>-0.3508857994262491</v>
       </c>
       <c r="J2" t="n">
+        <v>352</v>
+      </c>
+      <c r="K2" t="n">
         <v>349</v>
       </c>
-      <c r="K2" t="n">
-        <v>346</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.07930421061278747</v>
+        <v>0.07104528570126623</v>
       </c>
       <c r="M2" t="n">
-        <v>7.311394633527544</v>
+        <v>7.364427396702729</v>
       </c>
       <c r="N2" t="n">
-        <v>88.83204854961096</v>
+        <v>89.56085657009017</v>
       </c>
       <c r="O2" t="n">
-        <v>9.425075519570703</v>
+        <v>9.463659787317493</v>
       </c>
       <c r="P2" t="n">
-        <v>339.606435586281</v>
+        <v>339.3642760491121</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31615,28 +31879,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3003295212141178</v>
+        <v>-0.2875754210296895</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K3" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02388732544012873</v>
+        <v>0.02227451897292398</v>
       </c>
       <c r="M3" t="n">
-        <v>10.54901445501293</v>
+        <v>10.53527450519293</v>
       </c>
       <c r="N3" t="n">
-        <v>203.6327811689443</v>
+        <v>202.2933290085733</v>
       </c>
       <c r="O3" t="n">
-        <v>14.26999583633241</v>
+        <v>14.22298593856344</v>
       </c>
       <c r="P3" t="n">
-        <v>329.2835601874353</v>
+        <v>329.1407073649252</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31693,28 +31957,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1767837947722985</v>
+        <v>-0.1953110400081928</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005807968837482469</v>
+        <v>0.007203517074927279</v>
       </c>
       <c r="M4" t="n">
-        <v>12.3453275035001</v>
+        <v>12.30221173738878</v>
       </c>
       <c r="N4" t="n">
-        <v>295.1717861989806</v>
+        <v>292.5818965972657</v>
       </c>
       <c r="O4" t="n">
-        <v>17.18056419908789</v>
+        <v>17.10502547783153</v>
       </c>
       <c r="P4" t="n">
-        <v>336.729843573512</v>
+        <v>336.9375067776043</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31771,28 +32035,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5439041756823355</v>
+        <v>-0.5561962501562489</v>
       </c>
       <c r="J5" t="n">
+        <v>352</v>
+      </c>
+      <c r="K5" t="n">
         <v>349</v>
       </c>
-      <c r="K5" t="n">
-        <v>346</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.06349482721552901</v>
+        <v>0.0671438508963158</v>
       </c>
       <c r="M5" t="n">
-        <v>11.85693897613067</v>
+        <v>11.82940727098142</v>
       </c>
       <c r="N5" t="n">
-        <v>242.3032011827792</v>
+        <v>240.7466976649539</v>
       </c>
       <c r="O5" t="n">
-        <v>15.56609139067284</v>
+        <v>15.51601423255837</v>
       </c>
       <c r="P5" t="n">
-        <v>337.804344319815</v>
+        <v>337.9415832641059</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31849,28 +32113,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7362382806023643</v>
+        <v>-0.7459258854346628</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0908226513864977</v>
+        <v>0.09437960384297805</v>
       </c>
       <c r="M6" t="n">
-        <v>13.27062838941272</v>
+        <v>13.21579749404687</v>
       </c>
       <c r="N6" t="n">
-        <v>297.7147147476939</v>
+        <v>295.4717525165692</v>
       </c>
       <c r="O6" t="n">
-        <v>17.25441145758655</v>
+        <v>17.18929179799358</v>
       </c>
       <c r="P6" t="n">
-        <v>331.2664045792709</v>
+        <v>331.3755433291767</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31927,28 +32191,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09249443788749315</v>
+        <v>0.08008061781082372</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K7" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002467873951576771</v>
+        <v>0.001877914697813954</v>
       </c>
       <c r="M7" t="n">
-        <v>11.01356686815306</v>
+        <v>10.99287018479489</v>
       </c>
       <c r="N7" t="n">
-        <v>193.6607034023894</v>
+        <v>192.5281756427756</v>
       </c>
       <c r="O7" t="n">
-        <v>13.9162029089256</v>
+        <v>13.87545226804429</v>
       </c>
       <c r="P7" t="n">
-        <v>312.0343462494433</v>
+        <v>312.1721341536431</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32005,28 +32269,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4036751901764403</v>
+        <v>-0.4291974989116517</v>
       </c>
       <c r="J8" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K8" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03136169232750463</v>
+        <v>0.03563140166141221</v>
       </c>
       <c r="M8" t="n">
-        <v>12.88009574176557</v>
+        <v>12.92686831625817</v>
       </c>
       <c r="N8" t="n">
-        <v>281.941515377822</v>
+        <v>281.6912000814478</v>
       </c>
       <c r="O8" t="n">
-        <v>16.79111417916697</v>
+        <v>16.7836587215496</v>
       </c>
       <c r="P8" t="n">
-        <v>321.5720722231868</v>
+        <v>321.8553696272857</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32083,28 +32347,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2947747335594352</v>
+        <v>-0.3227244636635513</v>
       </c>
       <c r="J9" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K9" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02940489004482782</v>
+        <v>0.0350772096225257</v>
       </c>
       <c r="M9" t="n">
-        <v>9.625979563441994</v>
+        <v>9.733402949889529</v>
       </c>
       <c r="N9" t="n">
-        <v>158.459495850894</v>
+        <v>159.6616946163781</v>
       </c>
       <c r="O9" t="n">
-        <v>12.58806958397093</v>
+        <v>12.63573086989344</v>
       </c>
       <c r="P9" t="n">
-        <v>326.8185413343499</v>
+        <v>327.131507912716</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32161,28 +32425,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3990788875111943</v>
+        <v>-0.4205011860190397</v>
       </c>
       <c r="J10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K10" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03675550629002078</v>
+        <v>0.04105728415548715</v>
       </c>
       <c r="M10" t="n">
-        <v>12.92810524761817</v>
+        <v>12.94400331959202</v>
       </c>
       <c r="N10" t="n">
-        <v>231.3482817013055</v>
+        <v>230.8595461809747</v>
       </c>
       <c r="O10" t="n">
-        <v>15.21013746490496</v>
+        <v>15.1940628595835</v>
       </c>
       <c r="P10" t="n">
-        <v>322.2565897625083</v>
+        <v>322.496803657227</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32239,28 +32503,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2465670600015097</v>
+        <v>-0.2490847528207007</v>
       </c>
       <c r="J11" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K11" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01948624045450786</v>
+        <v>0.02021354516509011</v>
       </c>
       <c r="M11" t="n">
-        <v>10.79687661689966</v>
+        <v>10.7201539316363</v>
       </c>
       <c r="N11" t="n">
-        <v>168.9502977088507</v>
+        <v>167.5243728425563</v>
       </c>
       <c r="O11" t="n">
-        <v>12.99808823284604</v>
+        <v>12.9431206763499</v>
       </c>
       <c r="P11" t="n">
-        <v>322.4571619699262</v>
+        <v>322.4853823448221</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32317,28 +32581,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4536465100865738</v>
+        <v>-0.4533027807337168</v>
       </c>
       <c r="J12" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K12" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1422011046647184</v>
+        <v>0.144122254713948</v>
       </c>
       <c r="M12" t="n">
-        <v>6.778726867118031</v>
+        <v>6.725168912096802</v>
       </c>
       <c r="N12" t="n">
-        <v>68.58622195317803</v>
+        <v>68.0028141759062</v>
       </c>
       <c r="O12" t="n">
-        <v>8.281679899222018</v>
+        <v>8.246381883948025</v>
       </c>
       <c r="P12" t="n">
-        <v>337.5470288078669</v>
+        <v>337.5431727896944</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32395,28 +32659,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5448121960415216</v>
+        <v>-0.5843199166645385</v>
       </c>
       <c r="J13" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K13" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05439157244320336</v>
+        <v>0.06203522102440984</v>
       </c>
       <c r="M13" t="n">
-        <v>13.47563048200417</v>
+        <v>13.6420608295818</v>
       </c>
       <c r="N13" t="n">
-        <v>287.2238556329445</v>
+        <v>289.8154495077005</v>
       </c>
       <c r="O13" t="n">
-        <v>16.94767994838658</v>
+        <v>17.02396691455022</v>
       </c>
       <c r="P13" t="n">
-        <v>340.164371586987</v>
+        <v>340.6056847883558</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32473,28 +32737,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4167604465999734</v>
+        <v>-0.4288391915322793</v>
       </c>
       <c r="J14" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K14" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04306906419635537</v>
+        <v>0.04613762322132808</v>
       </c>
       <c r="M14" t="n">
-        <v>11.58261101458082</v>
+        <v>11.55746293498786</v>
       </c>
       <c r="N14" t="n">
-        <v>212.4267112062449</v>
+        <v>211.0676144101278</v>
       </c>
       <c r="O14" t="n">
-        <v>14.57486573544487</v>
+        <v>14.52816624389079</v>
       </c>
       <c r="P14" t="n">
-        <v>340.6386089836107</v>
+        <v>340.7746903604285</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32551,28 +32815,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3111186591401204</v>
+        <v>-0.3098003483799276</v>
       </c>
       <c r="J15" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K15" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04937767110561186</v>
+        <v>0.04977857243770101</v>
       </c>
       <c r="M15" t="n">
-        <v>7.25169531488243</v>
+        <v>7.199893704280146</v>
       </c>
       <c r="N15" t="n">
-        <v>102.9183317572479</v>
+        <v>102.0565672320196</v>
       </c>
       <c r="O15" t="n">
-        <v>10.14486726168696</v>
+        <v>10.1023050454844</v>
       </c>
       <c r="P15" t="n">
-        <v>344.2890957886622</v>
+        <v>344.274298864343</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32629,28 +32893,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8083330210956842</v>
+        <v>-0.7948040565650054</v>
       </c>
       <c r="J16" t="n">
+        <v>352</v>
+      </c>
+      <c r="K16" t="n">
         <v>349</v>
       </c>
-      <c r="K16" t="n">
-        <v>346</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1647151434173371</v>
+        <v>0.1619849516003717</v>
       </c>
       <c r="M16" t="n">
-        <v>10.87395346345107</v>
+        <v>10.83417283351707</v>
       </c>
       <c r="N16" t="n">
-        <v>182.860161823295</v>
+        <v>181.9065981997801</v>
       </c>
       <c r="O16" t="n">
-        <v>13.52257970297439</v>
+        <v>13.48727541795525</v>
       </c>
       <c r="P16" t="n">
-        <v>351.475226908585</v>
+        <v>351.3233271318535</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32707,28 +32971,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4814123966978192</v>
+        <v>-0.469728673763936</v>
       </c>
       <c r="J17" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K17" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1098503291651493</v>
+        <v>0.1063451428699564</v>
       </c>
       <c r="M17" t="n">
-        <v>7.946161765335493</v>
+        <v>7.935008932431187</v>
       </c>
       <c r="N17" t="n">
-        <v>103.9718819486153</v>
+        <v>103.5369719523323</v>
       </c>
       <c r="O17" t="n">
-        <v>10.19666033310001</v>
+        <v>10.17531188476954</v>
       </c>
       <c r="P17" t="n">
-        <v>346.5483800897306</v>
+        <v>346.4176060878297</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32785,28 +33049,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5668914149814359</v>
+        <v>-0.5564880484873977</v>
       </c>
       <c r="J18" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K18" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1262819780777131</v>
+        <v>0.1237808444891783</v>
       </c>
       <c r="M18" t="n">
-        <v>8.758765474625582</v>
+        <v>8.723827390613204</v>
       </c>
       <c r="N18" t="n">
-        <v>122.8425711028952</v>
+        <v>122.1632050337115</v>
       </c>
       <c r="O18" t="n">
-        <v>11.08343679112644</v>
+        <v>11.0527464927823</v>
       </c>
       <c r="P18" t="n">
-        <v>350.240425284576</v>
+        <v>350.1239222660951</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32863,28 +33127,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1726990639130172</v>
+        <v>-0.1519866702957395</v>
       </c>
       <c r="J19" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K19" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01702970612624344</v>
+        <v>0.0132757322727286</v>
       </c>
       <c r="M19" t="n">
-        <v>7.555413377967573</v>
+        <v>7.57054871996555</v>
       </c>
       <c r="N19" t="n">
-        <v>95.11136762451819</v>
+        <v>95.67924910240144</v>
       </c>
       <c r="O19" t="n">
-        <v>9.752505710047966</v>
+        <v>9.781577025326818</v>
       </c>
       <c r="P19" t="n">
-        <v>343.4987834660723</v>
+        <v>343.2668715444987</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32941,28 +33205,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2233568976156939</v>
+        <v>-0.1959734697424926</v>
       </c>
       <c r="J20" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K20" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02357023540349656</v>
+        <v>0.01817551078729496</v>
       </c>
       <c r="M20" t="n">
-        <v>8.67763184891683</v>
+        <v>8.731930121124206</v>
       </c>
       <c r="N20" t="n">
-        <v>114.1813166778008</v>
+        <v>115.6142144270756</v>
       </c>
       <c r="O20" t="n">
-        <v>10.68556580990454</v>
+        <v>10.75240505315325</v>
       </c>
       <c r="P20" t="n">
-        <v>347.4595430329209</v>
+        <v>347.1529421032536</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33019,28 +33283,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2098387866920982</v>
+        <v>0.2256304820760312</v>
       </c>
       <c r="J21" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K21" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02191439357281766</v>
+        <v>0.02549194490615936</v>
       </c>
       <c r="M21" t="n">
-        <v>7.590972857790628</v>
+        <v>7.618391792969454</v>
       </c>
       <c r="N21" t="n">
-        <v>108.5770813767334</v>
+        <v>108.454465352499</v>
       </c>
       <c r="O21" t="n">
-        <v>10.42003269556931</v>
+        <v>10.41414736560315</v>
       </c>
       <c r="P21" t="n">
-        <v>334.3767977461158</v>
+        <v>334.1999807957203</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33097,28 +33361,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4490142912183258</v>
+        <v>-0.4329526430259479</v>
       </c>
       <c r="J22" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K22" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1199974668194594</v>
+        <v>0.1132168948214149</v>
       </c>
       <c r="M22" t="n">
-        <v>7.138239709734159</v>
+        <v>7.147689059878735</v>
       </c>
       <c r="N22" t="n">
-        <v>81.57857429525833</v>
+        <v>81.70811416465823</v>
       </c>
       <c r="O22" t="n">
-        <v>9.032085821960415</v>
+        <v>9.039254071252683</v>
       </c>
       <c r="P22" t="n">
-        <v>356.293758268221</v>
+        <v>356.1136106767594</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33175,28 +33439,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2987404443803459</v>
+        <v>-0.299804496979873</v>
       </c>
       <c r="J23" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K23" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06463582386107491</v>
+        <v>0.0661191023959703</v>
       </c>
       <c r="M23" t="n">
-        <v>6.474678490935355</v>
+        <v>6.425635071292216</v>
       </c>
       <c r="N23" t="n">
-        <v>71.35340605149527</v>
+        <v>70.74736379409413</v>
       </c>
       <c r="O23" t="n">
-        <v>8.447094533121746</v>
+        <v>8.411145212995322</v>
       </c>
       <c r="P23" t="n">
-        <v>350.555532450568</v>
+        <v>350.567447128253</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33234,7 +33498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X350"/>
+  <dimension ref="A1:X353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75628,12 +75892,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>-37.75630313980555,174.82981136892562</t>
+          <t>-37.75629643273781,174.8298521532104</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>-37.755625800512036,174.82951931366694</t>
+          <t>-37.755605752629016,174.82964122095154</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -75732,6 +75996,372 @@
         </is>
       </c>
       <c r="X350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-37.75700931091414,174.82992806341363</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-37.75629224766667,174.82987760171105</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-37.75559160755732,174.82972723388826</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-37.75486496617701,174.8296836551178</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-37.75413691584643,174.8295833969886</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-37.753448018731824,174.82933139017706</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-37.75273344314684,174.82921945210148</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-37.75206682852261,174.8288947162359</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-37.75137186428307,174.82869500448592</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-37.75072071752294,174.8283092552566</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-37.75006250650144,174.82793988013083</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-37.74932619147602,174.82788307301334</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-37.74869733833759,174.82742547901685</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-37.748053263702786,174.8270244304795</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-37.74737641810815,174.82674631506114</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>-37.746710382441115,174.82643008741314</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>-37.74603708342187,174.82614405412818</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>-37.7453995385722,174.82574214491603</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>-37.744719713649694,174.8254986831648</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>-37.74400438252351,174.8254556969759</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>-37.74331298637131,174.8252397966052</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>-37.74259176032189,174.8252199935434</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-37.75700978607564,174.82992517403662</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-37.756286966062596,174.8299097179367</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-37.75557539730203,174.82982580422586</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-37.75485842857703,174.82971925767475</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-37.754129629115994,174.82961712381808</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-37.753441221930814,174.82936104689335</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-37.752725809762175,174.82925258405382</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-37.75205555029452,174.82894305828162</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-37.751362811992955,174.82873352475687</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-37.75072357614808,174.8282971845264</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-37.75006487709679,174.82793035078993</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-37.74931183120486,174.82793852557708</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-37.74869733833759,174.82742547901685</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-37.748058586149625,174.82700405804766</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-37.74738521666549,174.82671340740492</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>-37.746718012388634,174.82640195305694</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>-37.74604238358103,174.82612451057582</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>-37.745400888253464,174.8257359043855</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>-37.7447211064692,174.8254894299142</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>-37.74400726553455,174.82543525199043</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>-37.74331132763968,174.8252508340229</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>-37.74259200435113,174.82521843501354</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-37.757009585045786,174.82992639646537</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-37.75628881188369,174.8298984939276</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-37.75557539730203,174.82982580422586</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-37.75485412431288,174.82974269786385</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-37.75412716865942,174.82962851209658</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-37.753439022964216,174.8293706417121</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-37.75272176707777,174.82927013090725</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-37.75205229890984,174.82895699472434</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-37.75136122656234,174.828740271244</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-37.750721567384595,174.82830566666124</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-37.750065846885576,174.827926452423</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-37.7493071096315,174.82795675802993</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-37.74869102436979,174.82744986071643</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-37.7480622470899,174.82699004526208</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-37.74738941466679,174.8266977063635</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>-37.74671978882585,174.8263954026907</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>-37.74604884860602,174.8261006717333</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>-37.74540365865085,174.8257230948747</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>-37.744722163669046,174.82548240636228</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>-37.74400676140172,174.82543882706997</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>-37.743311729756535,174.82524815828535</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>-37.74259135941665,174.82522255398536</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X353"/>
+  <dimension ref="A1:X354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27844,7 +27844,7 @@
         <v>330.02</v>
       </c>
       <c r="D353" t="n">
-        <v>321.16</v>
+        <v>318.9</v>
       </c>
       <c r="E353" t="n">
         <v>313.02</v>
@@ -27906,6 +27906,84 @@
       <c r="X353" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="C354" t="n">
+        <v>328.36</v>
+      </c>
+      <c r="D354" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="E354" t="n">
+        <v>310.98</v>
+      </c>
+      <c r="F354" t="n">
+        <v>302.36</v>
+      </c>
+      <c r="G354" t="n">
+        <v>304.04</v>
+      </c>
+      <c r="H354" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="I354" t="n">
+        <v>299.18</v>
+      </c>
+      <c r="J354" t="n">
+        <v>296.62</v>
+      </c>
+      <c r="K354" t="n">
+        <v>314.09</v>
+      </c>
+      <c r="L354" t="n">
+        <v>327.89</v>
+      </c>
+      <c r="M354" t="n">
+        <v>298.28</v>
+      </c>
+      <c r="N354" t="n">
+        <v>320.43</v>
+      </c>
+      <c r="O354" t="n">
+        <v>341.01</v>
+      </c>
+      <c r="P354" t="n">
+        <v>344.13</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>342.08</v>
+      </c>
+      <c r="R354" t="n">
+        <v>346.43</v>
+      </c>
+      <c r="S354" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="T354" t="n">
+        <v>361.26</v>
+      </c>
+      <c r="U354" t="n">
+        <v>350.24</v>
+      </c>
+      <c r="V354" t="n">
+        <v>354.18</v>
+      </c>
+      <c r="W354" t="n">
+        <v>343.28</v>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27920,7 +27998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B371"/>
+  <dimension ref="A1:B372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31633,6 +31711,16 @@
       </c>
       <c r="B371" t="n">
         <v>0.98</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
@@ -31801,28 +31889,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3508857994262491</v>
+        <v>-0.344237526960216</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07104528570126623</v>
+        <v>0.06861140112726505</v>
       </c>
       <c r="M2" t="n">
-        <v>7.364427396702729</v>
+        <v>7.380686164052507</v>
       </c>
       <c r="N2" t="n">
-        <v>89.56085657009017</v>
+        <v>89.74042086505344</v>
       </c>
       <c r="O2" t="n">
-        <v>9.463659787317493</v>
+        <v>9.473142079851513</v>
       </c>
       <c r="P2" t="n">
-        <v>339.3642760491121</v>
+        <v>339.2894732576329</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31879,28 +31967,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2875754210296895</v>
+        <v>-0.2838341385921243</v>
       </c>
       <c r="J3" t="n">
+        <v>353</v>
+      </c>
+      <c r="K3" t="n">
         <v>352</v>
       </c>
-      <c r="K3" t="n">
-        <v>351</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02227451897292398</v>
+        <v>0.02181710633364387</v>
       </c>
       <c r="M3" t="n">
-        <v>10.53527450519293</v>
+        <v>10.5276305087742</v>
       </c>
       <c r="N3" t="n">
-        <v>202.2933290085733</v>
+        <v>201.8565213693128</v>
       </c>
       <c r="O3" t="n">
-        <v>14.22298593856344</v>
+        <v>14.20762194631152</v>
       </c>
       <c r="P3" t="n">
-        <v>329.1407073649252</v>
+        <v>329.098736548222</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31957,28 +32045,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1953110400081928</v>
+        <v>-0.206008109054236</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007203517074927279</v>
+        <v>0.008024512157101316</v>
       </c>
       <c r="M4" t="n">
-        <v>12.30221173738878</v>
+        <v>12.33921692988974</v>
       </c>
       <c r="N4" t="n">
-        <v>292.5818965972657</v>
+        <v>292.7824776499457</v>
       </c>
       <c r="O4" t="n">
-        <v>17.10502547783153</v>
+        <v>17.11088769321877</v>
       </c>
       <c r="P4" t="n">
-        <v>336.9375067776043</v>
+        <v>337.0577111415252</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32035,28 +32123,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5561962501562489</v>
+        <v>-0.562582443285786</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0671438508963158</v>
+        <v>0.06884414588695276</v>
       </c>
       <c r="M5" t="n">
-        <v>11.82940727098142</v>
+        <v>11.83418826928008</v>
       </c>
       <c r="N5" t="n">
-        <v>240.7466976649539</v>
+        <v>240.4614051895659</v>
       </c>
       <c r="O5" t="n">
-        <v>15.51601423255837</v>
+        <v>15.50681802271394</v>
       </c>
       <c r="P5" t="n">
-        <v>337.9415832641059</v>
+        <v>338.0130085837399</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32113,28 +32201,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7459258854346628</v>
+        <v>-0.7506974524857029</v>
       </c>
       <c r="J6" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K6" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09437960384297805</v>
+        <v>0.09590151690226967</v>
       </c>
       <c r="M6" t="n">
-        <v>13.21579749404687</v>
+        <v>13.20710642125533</v>
       </c>
       <c r="N6" t="n">
-        <v>295.4717525165692</v>
+        <v>294.8470102822045</v>
       </c>
       <c r="O6" t="n">
-        <v>17.18929179799358</v>
+        <v>17.17110975686209</v>
       </c>
       <c r="P6" t="n">
-        <v>331.3755433291767</v>
+        <v>331.4293923956109</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32191,28 +32279,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08008061781082372</v>
+        <v>0.07462107630559978</v>
       </c>
       <c r="J7" t="n">
+        <v>353</v>
+      </c>
+      <c r="K7" t="n">
         <v>352</v>
       </c>
-      <c r="K7" t="n">
-        <v>351</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.001877914697813954</v>
+        <v>0.001637653871061628</v>
       </c>
       <c r="M7" t="n">
-        <v>10.99287018479489</v>
+        <v>10.99406721681385</v>
       </c>
       <c r="N7" t="n">
-        <v>192.5281756427756</v>
+        <v>192.2798349657514</v>
       </c>
       <c r="O7" t="n">
-        <v>13.87545226804429</v>
+        <v>13.86650045850616</v>
       </c>
       <c r="P7" t="n">
-        <v>312.1721341536431</v>
+        <v>312.2328439391821</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32269,28 +32357,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4291974989116517</v>
+        <v>-0.4385459232513498</v>
       </c>
       <c r="J8" t="n">
+        <v>353</v>
+      </c>
+      <c r="K8" t="n">
         <v>352</v>
       </c>
-      <c r="K8" t="n">
-        <v>351</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03563140166141221</v>
+        <v>0.03723223287668664</v>
       </c>
       <c r="M8" t="n">
-        <v>12.92686831625817</v>
+        <v>12.94794847958024</v>
       </c>
       <c r="N8" t="n">
-        <v>281.6912000814478</v>
+        <v>281.767791719503</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7836587215496</v>
+        <v>16.78594029893777</v>
       </c>
       <c r="P8" t="n">
-        <v>321.8553696272857</v>
+        <v>321.9593339155464</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32347,28 +32435,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3227244636635513</v>
+        <v>-0.3330030235874195</v>
       </c>
       <c r="J9" t="n">
+        <v>353</v>
+      </c>
+      <c r="K9" t="n">
         <v>352</v>
       </c>
-      <c r="K9" t="n">
-        <v>351</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0350772096225257</v>
+        <v>0.03723177259851029</v>
       </c>
       <c r="M9" t="n">
-        <v>9.733402949889529</v>
+        <v>9.776174295005502</v>
       </c>
       <c r="N9" t="n">
-        <v>159.6616946163781</v>
+        <v>160.2488788488681</v>
       </c>
       <c r="O9" t="n">
-        <v>12.63573086989344</v>
+        <v>12.65894461828742</v>
       </c>
       <c r="P9" t="n">
-        <v>327.131507912716</v>
+        <v>327.2468158483603</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32425,28 +32513,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4205011860190397</v>
+        <v>-0.4282719716474328</v>
       </c>
       <c r="J10" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K10" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04105728415548715</v>
+        <v>0.04264734151635852</v>
       </c>
       <c r="M10" t="n">
-        <v>12.94400331959202</v>
+        <v>12.95310003451431</v>
       </c>
       <c r="N10" t="n">
-        <v>230.8595461809747</v>
+        <v>230.7953210338953</v>
       </c>
       <c r="O10" t="n">
-        <v>15.1940628595835</v>
+        <v>15.19194921772369</v>
       </c>
       <c r="P10" t="n">
-        <v>322.496803657227</v>
+        <v>322.5841043189598</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32503,28 +32591,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2490847528207007</v>
+        <v>-0.2499721241838934</v>
       </c>
       <c r="J11" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K11" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02021354516509011</v>
+        <v>0.02046694169084384</v>
       </c>
       <c r="M11" t="n">
-        <v>10.7201539316363</v>
+        <v>10.69514985581239</v>
       </c>
       <c r="N11" t="n">
-        <v>167.5243728425563</v>
+        <v>167.0548576211129</v>
       </c>
       <c r="O11" t="n">
-        <v>12.9431206763499</v>
+        <v>12.92497031412888</v>
       </c>
       <c r="P11" t="n">
-        <v>322.4853823448221</v>
+        <v>322.4953490841869</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32581,28 +32669,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4533027807337168</v>
+        <v>-0.4519082574595233</v>
       </c>
       <c r="J12" t="n">
+        <v>353</v>
+      </c>
+      <c r="K12" t="n">
         <v>352</v>
       </c>
-      <c r="K12" t="n">
-        <v>351</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.144122254713948</v>
+        <v>0.1440250972095289</v>
       </c>
       <c r="M12" t="n">
-        <v>6.725168912096802</v>
+        <v>6.71203241772778</v>
       </c>
       <c r="N12" t="n">
-        <v>68.0028141759062</v>
+        <v>67.82878196582429</v>
       </c>
       <c r="O12" t="n">
-        <v>8.246381883948025</v>
+        <v>8.23582308976002</v>
       </c>
       <c r="P12" t="n">
-        <v>337.5431727896944</v>
+        <v>337.5275286137451</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32659,28 +32747,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5843199166645385</v>
+        <v>-0.598605643712609</v>
       </c>
       <c r="J13" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K13" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06203522102440984</v>
+        <v>0.06482971088828948</v>
       </c>
       <c r="M13" t="n">
-        <v>13.6420608295818</v>
+        <v>13.70496404066715</v>
       </c>
       <c r="N13" t="n">
-        <v>289.8154495077005</v>
+        <v>290.9928801083757</v>
       </c>
       <c r="O13" t="n">
-        <v>17.02396691455022</v>
+        <v>17.05851342023612</v>
       </c>
       <c r="P13" t="n">
-        <v>340.6056847883558</v>
+        <v>340.7655643308649</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32737,28 +32825,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4288391915322793</v>
+        <v>-0.4335447338599333</v>
       </c>
       <c r="J14" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K14" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04613762322132808</v>
+        <v>0.04731472680395166</v>
       </c>
       <c r="M14" t="n">
-        <v>11.55746293498786</v>
+        <v>11.55352034613947</v>
       </c>
       <c r="N14" t="n">
-        <v>211.0676144101278</v>
+        <v>210.6791372919959</v>
       </c>
       <c r="O14" t="n">
-        <v>14.52816624389079</v>
+        <v>14.51479029445469</v>
       </c>
       <c r="P14" t="n">
-        <v>340.7746903604285</v>
+        <v>340.8278037985215</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32815,28 +32903,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3098003483799276</v>
+        <v>-0.3070630019157426</v>
       </c>
       <c r="J15" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K15" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04977857243770101</v>
+        <v>0.04917543245634315</v>
       </c>
       <c r="M15" t="n">
-        <v>7.199893704280146</v>
+        <v>7.1903121599813</v>
       </c>
       <c r="N15" t="n">
-        <v>102.0565672320196</v>
+        <v>101.8396718481869</v>
       </c>
       <c r="O15" t="n">
-        <v>10.1023050454844</v>
+        <v>10.0915643905287</v>
       </c>
       <c r="P15" t="n">
-        <v>344.274298864343</v>
+        <v>344.2435536545116</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32893,28 +32981,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7948040565650054</v>
+        <v>-0.7871366872473444</v>
       </c>
       <c r="J16" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K16" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1619849516003717</v>
+        <v>0.1596996062366132</v>
       </c>
       <c r="M16" t="n">
-        <v>10.83417283351707</v>
+        <v>10.83398467984873</v>
       </c>
       <c r="N16" t="n">
-        <v>181.9065981997801</v>
+        <v>181.966464537513</v>
       </c>
       <c r="O16" t="n">
-        <v>13.48727541795525</v>
+        <v>13.4894945990394</v>
       </c>
       <c r="P16" t="n">
-        <v>351.3233271318535</v>
+        <v>351.237085143135</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32971,28 +33059,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.469728673763936</v>
+        <v>-0.4652531205307896</v>
       </c>
       <c r="J17" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K17" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1063451428699564</v>
+        <v>0.1048891230527981</v>
       </c>
       <c r="M17" t="n">
-        <v>7.935008932431187</v>
+        <v>7.934567958286299</v>
       </c>
       <c r="N17" t="n">
-        <v>103.5369719523323</v>
+        <v>103.4399858698519</v>
       </c>
       <c r="O17" t="n">
-        <v>10.17531188476954</v>
+        <v>10.1705450134126</v>
       </c>
       <c r="P17" t="n">
-        <v>346.4176060878297</v>
+        <v>346.3674203856833</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33049,28 +33137,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5564880484873977</v>
+        <v>-0.5504126370045689</v>
       </c>
       <c r="J18" t="n">
+        <v>353</v>
+      </c>
+      <c r="K18" t="n">
         <v>352</v>
       </c>
-      <c r="K18" t="n">
-        <v>351</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1237808444891783</v>
+        <v>0.1217050264585106</v>
       </c>
       <c r="M18" t="n">
-        <v>8.723827390613204</v>
+        <v>8.722178473509324</v>
       </c>
       <c r="N18" t="n">
-        <v>122.1632050337115</v>
+        <v>122.1797648361965</v>
       </c>
       <c r="O18" t="n">
-        <v>11.0527464927823</v>
+        <v>11.05349559353042</v>
       </c>
       <c r="P18" t="n">
-        <v>350.1239222660951</v>
+        <v>350.0557664970512</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33127,28 +33215,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1519866702957395</v>
+        <v>-0.1434208171009211</v>
       </c>
       <c r="J19" t="n">
+        <v>353</v>
+      </c>
+      <c r="K19" t="n">
         <v>352</v>
       </c>
-      <c r="K19" t="n">
-        <v>351</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.0132757322727286</v>
+        <v>0.01181659793873058</v>
       </c>
       <c r="M19" t="n">
-        <v>7.57054871996555</v>
+        <v>7.583107619366142</v>
       </c>
       <c r="N19" t="n">
-        <v>95.67924910240144</v>
+        <v>96.13025426345853</v>
       </c>
       <c r="O19" t="n">
-        <v>9.781577025326818</v>
+        <v>9.804603728017698</v>
       </c>
       <c r="P19" t="n">
-        <v>343.2668715444987</v>
+        <v>343.1707772612294</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33205,28 +33293,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1959734697424926</v>
+        <v>-0.1855940488329105</v>
       </c>
       <c r="J20" t="n">
+        <v>353</v>
+      </c>
+      <c r="K20" t="n">
         <v>352</v>
       </c>
-      <c r="K20" t="n">
-        <v>351</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.01817551078729496</v>
+        <v>0.01627558993942702</v>
       </c>
       <c r="M20" t="n">
-        <v>8.731930121124206</v>
+        <v>8.756033984484842</v>
       </c>
       <c r="N20" t="n">
-        <v>115.6142144270756</v>
+        <v>116.347059375721</v>
       </c>
       <c r="O20" t="n">
-        <v>10.75240505315325</v>
+        <v>10.78642940809057</v>
       </c>
       <c r="P20" t="n">
-        <v>347.1529421032536</v>
+        <v>347.0365026791386</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33283,28 +33371,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2256304820760312</v>
+        <v>0.2309430931497149</v>
       </c>
       <c r="J21" t="n">
+        <v>353</v>
+      </c>
+      <c r="K21" t="n">
         <v>352</v>
       </c>
-      <c r="K21" t="n">
-        <v>351</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02549194490615936</v>
+        <v>0.02675444748006683</v>
       </c>
       <c r="M21" t="n">
-        <v>7.618391792969454</v>
+        <v>7.627880680408375</v>
       </c>
       <c r="N21" t="n">
-        <v>108.454465352499</v>
+        <v>108.4243950516252</v>
       </c>
       <c r="O21" t="n">
-        <v>10.41414736560315</v>
+        <v>10.41270354190616</v>
       </c>
       <c r="P21" t="n">
-        <v>334.1999807957203</v>
+        <v>334.1403823480462</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33361,28 +33449,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4329526430259479</v>
+        <v>-0.4277136331224121</v>
       </c>
       <c r="J22" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K22" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1132168948214149</v>
+        <v>0.1110261495898898</v>
       </c>
       <c r="M22" t="n">
-        <v>7.147689059878735</v>
+        <v>7.150303504657178</v>
       </c>
       <c r="N22" t="n">
-        <v>81.70811416465823</v>
+        <v>81.74553548248163</v>
       </c>
       <c r="O22" t="n">
-        <v>9.039254071252683</v>
+        <v>9.041323768258806</v>
       </c>
       <c r="P22" t="n">
-        <v>356.1136106767594</v>
+        <v>356.0547326555135</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33439,28 +33527,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.299804496979873</v>
+        <v>-0.2993668664257217</v>
       </c>
       <c r="J23" t="n">
+        <v>353</v>
+      </c>
+      <c r="K23" t="n">
         <v>352</v>
       </c>
-      <c r="K23" t="n">
-        <v>351</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.0661191023959703</v>
+        <v>0.06628654177342597</v>
       </c>
       <c r="M23" t="n">
-        <v>6.425635071292216</v>
+        <v>6.409418864500748</v>
       </c>
       <c r="N23" t="n">
-        <v>70.74736379409413</v>
+        <v>70.54826367406245</v>
       </c>
       <c r="O23" t="n">
-        <v>8.411145212995322</v>
+        <v>8.399301380118613</v>
       </c>
       <c r="P23" t="n">
-        <v>350.567447128253</v>
+        <v>350.5625376588188</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33498,7 +33586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X353"/>
+  <dimension ref="A1:X354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76263,7 +76351,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>-37.75557539730203,174.82982580422586</t>
+          <t>-37.75557126705487,174.82985091909592</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -76364,6 +76452,128 @@
       <c r="X353" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-37.75700841541728,174.8299335087779</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-37.756285778157384,174.82991694130857</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-37.755562202423086,174.82990603844618</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-37.75484998246943,174.8297652535148</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-37.754123974795924,174.82964329495692</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-37.753435949407354,174.82938405265094</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-37.75272176707777,174.82927013090725</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-37.75205229890984,174.82895699472434</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-37.75136122656234,174.828740271244</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-37.750721567384595,174.82830566666124</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-37.75007083052041,174.82790641914687</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-37.7493071096315,174.82795675802993</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-37.74869102436979,174.82744986071643</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-37.74807016034751,174.82695975608218</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-37.747401261070394,174.82665339930503</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>-37.74671978882585,174.8263954026907</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>-37.746057468632,174.82606888660317</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>-37.74540960197734,174.8256956146387</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>-37.74472575478927,174.8254585485811</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>-37.74400676140172,174.82543882706997</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>-37.74331211511847,174.8252455940368</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>-37.7425942354747,174.82520418559693</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X354"/>
+  <dimension ref="A1:X355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27934,25 +27934,25 @@
         <v>304.04</v>
       </c>
       <c r="H354" t="n">
-        <v>292.6</v>
+        <v>298.17</v>
       </c>
       <c r="I354" t="n">
-        <v>299.18</v>
+        <v>305.38</v>
       </c>
       <c r="J354" t="n">
-        <v>296.62</v>
+        <v>301.37</v>
       </c>
       <c r="K354" t="n">
-        <v>314.09</v>
+        <v>317.07</v>
       </c>
       <c r="L354" t="n">
         <v>327.89</v>
       </c>
       <c r="M354" t="n">
-        <v>298.28</v>
+        <v>303.15</v>
       </c>
       <c r="N354" t="n">
-        <v>320.43</v>
+        <v>325.1</v>
       </c>
       <c r="O354" t="n">
         <v>341.01</v>
@@ -27961,7 +27961,7 @@
         <v>344.13</v>
       </c>
       <c r="Q354" t="n">
-        <v>342.08</v>
+        <v>345.98</v>
       </c>
       <c r="R354" t="n">
         <v>346.43</v>
@@ -27982,6 +27982,84 @@
         <v>343.28</v>
       </c>
       <c r="X354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:05:47+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>340.69</v>
+      </c>
+      <c r="C355" t="n">
+        <v>325.75</v>
+      </c>
+      <c r="D355" t="n">
+        <v>309.88</v>
+      </c>
+      <c r="E355" t="n">
+        <v>303.21</v>
+      </c>
+      <c r="F355" t="n">
+        <v>293.85</v>
+      </c>
+      <c r="G355" t="n">
+        <v>296.29</v>
+      </c>
+      <c r="H355" t="n">
+        <v>296.88</v>
+      </c>
+      <c r="I355" t="n">
+        <v>304.38</v>
+      </c>
+      <c r="J355" t="n">
+        <v>300.66</v>
+      </c>
+      <c r="K355" t="n">
+        <v>315.73</v>
+      </c>
+      <c r="L355" t="n">
+        <v>328.78</v>
+      </c>
+      <c r="M355" t="n">
+        <v>299.83</v>
+      </c>
+      <c r="N355" t="n">
+        <v>323</v>
+      </c>
+      <c r="O355" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="P355" t="n">
+        <v>343.48</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>345.83</v>
+      </c>
+      <c r="R355" t="n">
+        <v>345.54</v>
+      </c>
+      <c r="S355" t="n">
+        <v>353.89</v>
+      </c>
+      <c r="T355" t="n">
+        <v>361.03</v>
+      </c>
+      <c r="U355" t="n">
+        <v>348.75</v>
+      </c>
+      <c r="V355" t="n">
+        <v>351.04</v>
+      </c>
+      <c r="W355" t="n">
+        <v>342.77</v>
+      </c>
+      <c r="X355" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27998,7 +28076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B372"/>
+  <dimension ref="A1:B373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31721,6 +31799,16 @@
       </c>
       <c r="B372" t="n">
         <v>-0.79</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -31889,28 +31977,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.344237526960216</v>
+        <v>-0.3385108083803515</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06861140112726505</v>
+        <v>0.06662264775104521</v>
       </c>
       <c r="M2" t="n">
-        <v>7.380686164052507</v>
+        <v>7.391976975379907</v>
       </c>
       <c r="N2" t="n">
-        <v>89.74042086505344</v>
+        <v>89.80972388097298</v>
       </c>
       <c r="O2" t="n">
-        <v>9.473142079851513</v>
+        <v>9.476799242411595</v>
       </c>
       <c r="P2" t="n">
-        <v>339.2894732576329</v>
+        <v>339.2249121692995</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31967,28 +32055,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2838341385921243</v>
+        <v>-0.2815231376420846</v>
       </c>
       <c r="J3" t="n">
+        <v>354</v>
+      </c>
+      <c r="K3" t="n">
         <v>353</v>
       </c>
-      <c r="K3" t="n">
-        <v>352</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02181710633364387</v>
+        <v>0.02158413520194147</v>
       </c>
       <c r="M3" t="n">
-        <v>10.5276305087742</v>
+        <v>10.51148195795247</v>
       </c>
       <c r="N3" t="n">
-        <v>201.8565213693128</v>
+        <v>201.3376101007506</v>
       </c>
       <c r="O3" t="n">
-        <v>14.20762194631152</v>
+        <v>14.18934847344129</v>
       </c>
       <c r="P3" t="n">
-        <v>329.098736548222</v>
+        <v>329.0727601354443</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32045,28 +32133,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.206008109054236</v>
+        <v>-0.2175262502303986</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008024512157101316</v>
+        <v>0.008948831310398031</v>
       </c>
       <c r="M4" t="n">
-        <v>12.33921692988974</v>
+        <v>12.38244887342769</v>
       </c>
       <c r="N4" t="n">
-        <v>292.7824776499457</v>
+        <v>293.2643832638132</v>
       </c>
       <c r="O4" t="n">
-        <v>17.11088769321877</v>
+        <v>17.12496374489047</v>
       </c>
       <c r="P4" t="n">
-        <v>337.0577111415252</v>
+        <v>337.1874111508955</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32123,28 +32211,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.562582443285786</v>
+        <v>-0.5730148488171584</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06884414588695276</v>
+        <v>0.0713143358934355</v>
       </c>
       <c r="M5" t="n">
-        <v>11.83418826928008</v>
+        <v>11.86305182024187</v>
       </c>
       <c r="N5" t="n">
-        <v>240.4614051895659</v>
+        <v>240.856940622491</v>
       </c>
       <c r="O5" t="n">
-        <v>15.50681802271394</v>
+        <v>15.51956637997631</v>
       </c>
       <c r="P5" t="n">
-        <v>338.0130085837399</v>
+        <v>338.1299185448142</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32201,28 +32289,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7506974524857029</v>
+        <v>-0.7599635170520346</v>
       </c>
       <c r="J6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09590151690226967</v>
+        <v>0.09829818806273205</v>
       </c>
       <c r="M6" t="n">
-        <v>13.20710642125533</v>
+        <v>13.22598141291648</v>
       </c>
       <c r="N6" t="n">
-        <v>294.8470102822045</v>
+        <v>294.8462379726308</v>
       </c>
       <c r="O6" t="n">
-        <v>17.17110975686209</v>
+        <v>17.17108726821429</v>
       </c>
       <c r="P6" t="n">
-        <v>331.4293923956109</v>
+        <v>331.5341688119821</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32279,28 +32367,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07462107630559978</v>
+        <v>0.06513772349128996</v>
       </c>
       <c r="J7" t="n">
+        <v>354</v>
+      </c>
+      <c r="K7" t="n">
         <v>353</v>
       </c>
-      <c r="K7" t="n">
-        <v>352</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.001637653871061628</v>
+        <v>0.001249471201344221</v>
       </c>
       <c r="M7" t="n">
-        <v>10.99406721681385</v>
+        <v>11.01938013318755</v>
       </c>
       <c r="N7" t="n">
-        <v>192.2798349657514</v>
+        <v>192.6413992979664</v>
       </c>
       <c r="O7" t="n">
-        <v>13.86650045850616</v>
+        <v>13.87953166709765</v>
       </c>
       <c r="P7" t="n">
-        <v>312.2328439391821</v>
+        <v>312.3385079217419</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32357,28 +32445,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4385459232513498</v>
+        <v>-0.442583520766492</v>
       </c>
       <c r="J8" t="n">
+        <v>354</v>
+      </c>
+      <c r="K8" t="n">
         <v>353</v>
       </c>
-      <c r="K8" t="n">
-        <v>352</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03723223287668664</v>
+        <v>0.0380964278008743</v>
       </c>
       <c r="M8" t="n">
-        <v>12.94794847958024</v>
+        <v>12.93607691430816</v>
       </c>
       <c r="N8" t="n">
-        <v>281.767791719503</v>
+        <v>280.9975733564935</v>
       </c>
       <c r="O8" t="n">
-        <v>16.78594029893777</v>
+        <v>16.76298223337642</v>
       </c>
       <c r="P8" t="n">
-        <v>321.9593339155464</v>
+        <v>322.0043909010959</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32435,28 +32523,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3330030235874195</v>
+        <v>-0.3370864216456771</v>
       </c>
       <c r="J9" t="n">
+        <v>354</v>
+      </c>
+      <c r="K9" t="n">
         <v>353</v>
       </c>
-      <c r="K9" t="n">
-        <v>352</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03723177259851029</v>
+        <v>0.03832716650118217</v>
       </c>
       <c r="M9" t="n">
-        <v>9.776174295005502</v>
+        <v>9.77617635349435</v>
       </c>
       <c r="N9" t="n">
-        <v>160.2488788488681</v>
+        <v>159.7758142702044</v>
       </c>
       <c r="O9" t="n">
-        <v>12.65894461828742</v>
+        <v>12.64024581526026</v>
       </c>
       <c r="P9" t="n">
-        <v>327.2468158483603</v>
+        <v>327.2927876362128</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32513,28 +32601,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4282719716474328</v>
+        <v>-0.4312532758549134</v>
       </c>
       <c r="J10" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K10" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04264734151635852</v>
+        <v>0.04345430592996791</v>
       </c>
       <c r="M10" t="n">
-        <v>12.95310003451431</v>
+        <v>12.93355266602577</v>
       </c>
       <c r="N10" t="n">
-        <v>230.7953210338953</v>
+        <v>230.1115593591594</v>
       </c>
       <c r="O10" t="n">
-        <v>15.19194921772369</v>
+        <v>15.16942844536864</v>
       </c>
       <c r="P10" t="n">
-        <v>322.5841043189598</v>
+        <v>322.6177214189769</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32591,28 +32679,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2499721241838934</v>
+        <v>-0.2483874440727369</v>
       </c>
       <c r="J11" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K11" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02046694169084384</v>
+        <v>0.02032570869156314</v>
       </c>
       <c r="M11" t="n">
-        <v>10.69514985581239</v>
+        <v>10.66236825499646</v>
       </c>
       <c r="N11" t="n">
-        <v>167.0548576211129</v>
+        <v>166.5774739923563</v>
       </c>
       <c r="O11" t="n">
-        <v>12.92497031412888</v>
+        <v>12.90648960764918</v>
       </c>
       <c r="P11" t="n">
-        <v>322.4953490841869</v>
+        <v>322.4775506036992</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32669,28 +32757,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4519082574595233</v>
+        <v>-0.4500466906090563</v>
       </c>
       <c r="J12" t="n">
+        <v>354</v>
+      </c>
+      <c r="K12" t="n">
         <v>353</v>
       </c>
-      <c r="K12" t="n">
-        <v>352</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1440250972095289</v>
+        <v>0.1436404540341513</v>
       </c>
       <c r="M12" t="n">
-        <v>6.71203241772778</v>
+        <v>6.700924542028133</v>
       </c>
       <c r="N12" t="n">
-        <v>67.82878196582429</v>
+        <v>67.67097074288083</v>
       </c>
       <c r="O12" t="n">
-        <v>8.23582308976002</v>
+        <v>8.226236730296595</v>
       </c>
       <c r="P12" t="n">
-        <v>337.5275286137451</v>
+        <v>337.5066039884566</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32747,28 +32835,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.598605643712609</v>
+        <v>-0.6092632687287116</v>
       </c>
       <c r="J13" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K13" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06482971088828948</v>
+        <v>0.06712448513740921</v>
       </c>
       <c r="M13" t="n">
-        <v>13.70496404066715</v>
+        <v>13.74121534213266</v>
       </c>
       <c r="N13" t="n">
-        <v>290.9928801083757</v>
+        <v>291.2359285219465</v>
       </c>
       <c r="O13" t="n">
-        <v>17.05851342023612</v>
+        <v>17.06563589562213</v>
       </c>
       <c r="P13" t="n">
-        <v>340.7655643308649</v>
+        <v>340.8851359145354</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32825,28 +32913,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4335447338599333</v>
+        <v>-0.4343088887255245</v>
       </c>
       <c r="J14" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K14" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04731472680395166</v>
+        <v>0.04774235100018609</v>
       </c>
       <c r="M14" t="n">
-        <v>11.55352034613947</v>
+        <v>11.52510799134691</v>
       </c>
       <c r="N14" t="n">
-        <v>210.6791372919959</v>
+        <v>210.0116558753269</v>
       </c>
       <c r="O14" t="n">
-        <v>14.51479029445469</v>
+        <v>14.49177890651548</v>
       </c>
       <c r="P14" t="n">
-        <v>340.8278037985215</v>
+        <v>340.836502455087</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32903,28 +32991,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3070630019157426</v>
+        <v>-0.3043050356026488</v>
       </c>
       <c r="J15" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K15" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04917543245634315</v>
+        <v>0.04856405624985671</v>
       </c>
       <c r="M15" t="n">
-        <v>7.1903121599813</v>
+        <v>7.180812744511584</v>
       </c>
       <c r="N15" t="n">
-        <v>101.8396718481869</v>
+        <v>101.625772420523</v>
       </c>
       <c r="O15" t="n">
-        <v>10.0915643905287</v>
+        <v>10.08096088775881</v>
       </c>
       <c r="P15" t="n">
-        <v>344.2435536545116</v>
+        <v>344.212515843329</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32981,28 +33069,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7871366872473444</v>
+        <v>-0.7798941332936035</v>
       </c>
       <c r="J16" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K16" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1596996062366132</v>
+        <v>0.1576011175302235</v>
       </c>
       <c r="M16" t="n">
-        <v>10.83398467984873</v>
+        <v>10.83196494880464</v>
       </c>
       <c r="N16" t="n">
-        <v>181.966464537513</v>
+        <v>181.9681952801429</v>
       </c>
       <c r="O16" t="n">
-        <v>13.4894945990394</v>
+        <v>13.48955875038702</v>
       </c>
       <c r="P16" t="n">
-        <v>351.237085143135</v>
+        <v>351.1554606366103</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33059,28 +33147,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4652531205307896</v>
+        <v>-0.4567609541976174</v>
       </c>
       <c r="J17" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K17" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1048891230527981</v>
+        <v>0.1014340448688479</v>
       </c>
       <c r="M17" t="n">
-        <v>7.934567958286299</v>
+        <v>7.954321053041644</v>
       </c>
       <c r="N17" t="n">
-        <v>103.4399858698519</v>
+        <v>103.7810600403956</v>
       </c>
       <c r="O17" t="n">
-        <v>10.1705450134126</v>
+        <v>10.1872989570541</v>
       </c>
       <c r="P17" t="n">
-        <v>346.3674203856833</v>
+        <v>346.2720534540713</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33137,28 +33225,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5504126370045689</v>
+        <v>-0.5448760175939557</v>
       </c>
       <c r="J18" t="n">
+        <v>354</v>
+      </c>
+      <c r="K18" t="n">
         <v>353</v>
       </c>
-      <c r="K18" t="n">
-        <v>352</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1217050264585106</v>
+        <v>0.1198920953548134</v>
       </c>
       <c r="M18" t="n">
-        <v>8.722178473509324</v>
+        <v>8.718589134714088</v>
       </c>
       <c r="N18" t="n">
-        <v>122.1797648361965</v>
+        <v>122.1373927353397</v>
       </c>
       <c r="O18" t="n">
-        <v>11.05349559353042</v>
+        <v>11.05157874402294</v>
       </c>
       <c r="P18" t="n">
-        <v>350.0557664970512</v>
+        <v>349.9935330690639</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33215,28 +33303,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1434208171009211</v>
+        <v>-0.135642020507919</v>
       </c>
       <c r="J19" t="n">
+        <v>354</v>
+      </c>
+      <c r="K19" t="n">
         <v>353</v>
       </c>
-      <c r="K19" t="n">
-        <v>352</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01181659793873058</v>
+        <v>0.01057651424408157</v>
       </c>
       <c r="M19" t="n">
-        <v>7.583107619366142</v>
+        <v>7.59233041499053</v>
       </c>
       <c r="N19" t="n">
-        <v>96.13025426345853</v>
+        <v>96.45750952440584</v>
       </c>
       <c r="O19" t="n">
-        <v>9.804603728017698</v>
+        <v>9.82127840580878</v>
       </c>
       <c r="P19" t="n">
-        <v>343.1707772612294</v>
+        <v>343.0833410223087</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33293,28 +33381,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1855940488329105</v>
+        <v>-0.1754676800702449</v>
       </c>
       <c r="J20" t="n">
+        <v>354</v>
+      </c>
+      <c r="K20" t="n">
         <v>353</v>
       </c>
-      <c r="K20" t="n">
-        <v>352</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.01627558993942702</v>
+        <v>0.0145289971437973</v>
       </c>
       <c r="M20" t="n">
-        <v>8.756033984484842</v>
+        <v>8.779720656593797</v>
       </c>
       <c r="N20" t="n">
-        <v>116.347059375721</v>
+        <v>117.0335468908358</v>
       </c>
       <c r="O20" t="n">
-        <v>10.78642940809057</v>
+        <v>10.81820442082861</v>
       </c>
       <c r="P20" t="n">
-        <v>347.0365026791386</v>
+        <v>346.9226789548717</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33371,28 +33459,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2309430931497149</v>
+        <v>0.2353921364324041</v>
       </c>
       <c r="J21" t="n">
+        <v>354</v>
+      </c>
+      <c r="K21" t="n">
         <v>353</v>
       </c>
-      <c r="K21" t="n">
-        <v>352</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02675444748006683</v>
+        <v>0.0278698167501501</v>
       </c>
       <c r="M21" t="n">
-        <v>7.627880680408375</v>
+        <v>7.632260180158245</v>
       </c>
       <c r="N21" t="n">
-        <v>108.4243950516252</v>
+        <v>108.3133786518073</v>
       </c>
       <c r="O21" t="n">
-        <v>10.41270354190616</v>
+        <v>10.40737136129038</v>
       </c>
       <c r="P21" t="n">
-        <v>334.1403823480462</v>
+        <v>334.0903736343869</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33449,28 +33537,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4277136331224121</v>
+        <v>-0.4242050483593364</v>
       </c>
       <c r="J22" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K22" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1110261495898898</v>
+        <v>0.1098147823749656</v>
       </c>
       <c r="M22" t="n">
-        <v>7.150303504657178</v>
+        <v>7.145461305255186</v>
       </c>
       <c r="N22" t="n">
-        <v>81.74553548248163</v>
+        <v>81.63519909166321</v>
       </c>
       <c r="O22" t="n">
-        <v>9.041323768258806</v>
+        <v>9.035219924919549</v>
       </c>
       <c r="P22" t="n">
-        <v>356.0547326555135</v>
+        <v>356.0152242426814</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33527,28 +33615,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2993668664257217</v>
+        <v>-0.2991986511176782</v>
       </c>
       <c r="J23" t="n">
+        <v>354</v>
+      </c>
+      <c r="K23" t="n">
         <v>353</v>
       </c>
-      <c r="K23" t="n">
-        <v>352</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06628654177342597</v>
+        <v>0.06656632717268751</v>
       </c>
       <c r="M23" t="n">
-        <v>6.409418864500748</v>
+        <v>6.392039757791741</v>
       </c>
       <c r="N23" t="n">
-        <v>70.54826367406245</v>
+        <v>70.34869061946206</v>
       </c>
       <c r="O23" t="n">
-        <v>8.399301380118613</v>
+        <v>8.387412629617197</v>
       </c>
       <c r="P23" t="n">
-        <v>350.5625376588188</v>
+        <v>350.560646863284</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33586,7 +33674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X354"/>
+  <dimension ref="A1:X355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76493,22 +76581,22 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>-37.75272176707777,174.82927013090725</t>
+          <t>-37.75273575324829,174.82920942532502</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>-37.75205229890984,174.82895699472434</t>
+          <t>-37.752068047789336,174.82888949006787</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>-37.75136122656234,174.828740271244</t>
+          <t>-37.75137337299688,174.82868858443982</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>-37.750721567384595,174.82830566666124</t>
+          <t>-37.75072924188801,174.82827326055374</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -76518,12 +76606,12 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>-37.7493071096315,174.82795675802993</t>
+          <t>-37.74932071557797,174.82790421835156</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>-37.74869102436979,174.82744986071643</t>
+          <t>-37.7487040713686,174.8273994790581</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -76538,7 +76626,7 @@
       </c>
       <c r="Q354" t="inlineStr">
         <is>
-          <t>-37.74671978882585,174.8263954026907</t>
+          <t>-37.746731146366855,174.82635352329228</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -76572,6 +76660,128 @@
         </is>
       </c>
       <c r="X354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:05:47+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-37.75700552789506,174.82995106729848</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-37.75628100825662,174.8299459459224</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-37.7555547825644,174.82995115629066</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-37.7548342068797,174.82985116398424</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-37.75410384158464,174.82973648169752</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-37.75341658346573,174.82946855244194</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-37.75273251408406,174.82922348460923</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-37.75206550765005,174.82890037791773</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-37.75137155742597,174.82869631025798</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-37.75072579093789,174.82828783242846</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-37.75007322805164,174.8278967815157</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-37.74931144006871,174.82794003595788</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-37.74869820441244,174.8274221346241</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-37.74807041379692,174.82695878596599</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-37.747399392100036,174.82666038949728</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>-37.74673070953864,174.82635513403864</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>-37.746054876800756,174.82607844361945</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>-37.7454065711184,174.8257096284648</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>-37.744725368827964,174.8254611127353</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>-37.74400441403184,174.82545547353345</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>-37.74330685408566,174.82528060160138</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>-37.74259334651162,174.82520986309896</t>
+        </is>
+      </c>
+      <c r="X355" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
